--- a/minutes/20260406/要件定義_確認事項一覧_第二回.xlsx
+++ b/minutes/20260406/要件定義_確認事項一覧_第二回.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sumou-no-oujisama/Dropbox/koo/project/東海鋼材工業様/minutes/20260406/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D3B1A6-2FD4-4A4F-9837-99B0E0326F31}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16518BB0-792C-C44D-AB13-8BADF9DA63B9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="50120" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="要件定義 確認事項一覧" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'要件定義 確認事項一覧'!$A$3:$H$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'要件定義 確認事項一覧'!$A$3:$H$66</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="219">
   <si>
     <t>請求書・納品書メール送信システム — 要件定義 確認事項一覧</t>
   </si>
@@ -390,6 +390,15 @@
     <t>対応不要。土日も動かす</t>
   </si>
   <si>
+    <t>D-15</t>
+  </si>
+  <si>
+    <t>同じ得意先に請求書と納品書が同時にある場合、メールを1通にまとめるか（PDF複数添付）、別々に2通送るか。1通にまとめることを推奨</t>
+  </si>
+  <si>
+    <t>1通にまとめると得意先の受信負荷が減るが、設計が複雑になる。2通なら設計はシンプル</t>
+  </si>
+  <si>
     <t>E. 帳票（PDF）</t>
   </si>
   <si>
@@ -663,20 +672,23 @@
     <t>テスト運用の開始時期に影響する。得意先のメールアドレス収集には時間がかかるため、早めに動き出していただきたい</t>
   </si>
   <si>
-    <t>D-15</t>
-  </si>
-  <si>
-    <t>同じ得意先に請求書と納品書が同時にある場合、メールを1通にまとめるか（PDF複数添付）、別々に2通送るか。1通にまとめることを推奨</t>
-  </si>
-  <si>
-    <t>1通にまとめると得意先の受信負荷が減るが、設計が複雑になる。2通なら設計はシンプル</t>
+    <t>J. 画面設計</t>
+  </si>
+  <si>
+    <t>J-1</t>
+  </si>
+  <si>
+    <t>処理済み一覧・検索結果のページングは1ページ100件でよいか</t>
+  </si>
+  <si>
+    <t>件数が多い場合の画面表示速度に影響する。多すぎると重く、少なすぎるとページ送りが煩雑</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -746,8 +758,21 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Meiryo"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Meiryo"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -778,8 +803,14 @@
         <bgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+        <bgColor rgb="FFD6E4F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -856,11 +887,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -880,22 +950,33 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1204,30 +1285,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="6" style="9" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="8" style="9" customWidth="1"/>
-    <col min="4" max="4" width="50" style="9" customWidth="1"/>
-    <col min="5" max="5" width="53.1640625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="10" style="9" customWidth="1"/>
-    <col min="7" max="7" width="15" style="9" customWidth="1"/>
-    <col min="8" max="8" width="20" style="9" customWidth="1"/>
+    <col min="1" max="1" width="6" style="10" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="8" style="10" customWidth="1"/>
+    <col min="4" max="4" width="50" style="10" customWidth="1"/>
+    <col min="5" max="5" width="53.1640625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="10" style="10" customWidth="1"/>
+    <col min="7" max="7" width="15" style="10" customWidth="1"/>
+    <col min="8" max="8" width="20" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1256,16 +1337,16 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="19" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="11" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
     </row>
     <row r="5" spans="1:8" ht="36" customHeight="1">
       <c r="A5" s="2">
@@ -1450,16 +1531,16 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="19" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="15"/>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1">
       <c r="A13" s="3">
@@ -1506,16 +1587,16 @@
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" ht="19" customHeight="1">
-      <c r="A15" s="8"/>
-      <c r="B15" s="11" t="s">
+      <c r="A15" s="7"/>
+      <c r="B15" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" spans="1:8" ht="36" customHeight="1">
       <c r="A16" s="2">
@@ -1622,16 +1703,16 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="19" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="11" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="15"/>
     </row>
     <row r="21" spans="1:8" ht="54" customHeight="1">
       <c r="A21" s="2">
@@ -1997,55 +2078,55 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="54">
-      <c r="A35" s="10">
+    <row r="35" spans="1:8" ht="54" customHeight="1">
+      <c r="A35" s="8">
         <v>52</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="F35" s="10" t="s">
+      <c r="C35" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F35" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
     </row>
     <row r="36" spans="1:8" ht="19" customHeight="1">
-      <c r="A36" s="8"/>
-      <c r="B36" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="13"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="15"/>
     </row>
     <row r="37" spans="1:8" ht="36" customHeight="1">
       <c r="A37" s="2">
         <v>28</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>13</v>
@@ -2054,7 +2135,7 @@
         <v>14</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="36" customHeight="1">
@@ -2062,16 +2143,16 @@
         <v>29</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>26</v>
@@ -2080,7 +2161,7 @@
         <v>14</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="36" customHeight="1">
@@ -2088,16 +2169,16 @@
         <v>30</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>26</v>
@@ -2106,45 +2187,43 @@
         <v>14</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="19" customHeight="1">
-      <c r="A40" s="8"/>
-      <c r="B40" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="13"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="15"/>
     </row>
     <row r="41" spans="1:8" ht="36" customHeight="1">
       <c r="A41" s="3">
         <v>31</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="36" customHeight="1">
@@ -2152,16 +2231,16 @@
         <v>32</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>13</v>
@@ -2170,7 +2249,7 @@
         <v>14</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="36" customHeight="1">
@@ -2178,16 +2257,16 @@
         <v>33</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>26</v>
@@ -2196,7 +2275,7 @@
         <v>14</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="36" customHeight="1">
@@ -2204,16 +2283,16 @@
         <v>34</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>26</v>
@@ -2222,36 +2301,36 @@
         <v>14</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="19" customHeight="1">
-      <c r="A45" s="8"/>
-      <c r="B45" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="13"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="15"/>
     </row>
     <row r="46" spans="1:8" ht="54" customHeight="1">
       <c r="A46" s="3">
         <v>35</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>44</v>
@@ -2260,7 +2339,7 @@
         <v>14</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="36" customHeight="1">
@@ -2268,16 +2347,16 @@
         <v>36</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>13</v>
@@ -2286,7 +2365,7 @@
         <v>14</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="54" customHeight="1">
@@ -2294,16 +2373,16 @@
         <v>37</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>26</v>
@@ -2312,7 +2391,7 @@
         <v>14</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="36" customHeight="1">
@@ -2320,16 +2399,16 @@
         <v>38</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>13</v>
@@ -2338,7 +2417,7 @@
         <v>14</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="36" customHeight="1">
@@ -2346,16 +2425,16 @@
         <v>39</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>26</v>
@@ -2364,36 +2443,36 @@
         <v>14</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="19" customHeight="1">
-      <c r="A51" s="8"/>
-      <c r="B51" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="13"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="15"/>
     </row>
     <row r="52" spans="1:8" ht="54" customHeight="1">
       <c r="A52" s="2">
         <v>40</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>26</v>
@@ -2402,7 +2481,7 @@
         <v>14</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="36" customHeight="1">
@@ -2410,16 +2489,16 @@
         <v>41</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>13</v>
@@ -2428,7 +2507,7 @@
         <v>14</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="36" customHeight="1">
@@ -2436,16 +2515,16 @@
         <v>42</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>13</v>
@@ -2458,32 +2537,32 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="19" customHeight="1">
-      <c r="A55" s="7"/>
-      <c r="B55" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="13"/>
+      <c r="A55" s="9"/>
+      <c r="B55" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="15"/>
     </row>
     <row r="56" spans="1:8" ht="40" customHeight="1">
       <c r="A56" s="5">
         <v>43</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>13</v>
@@ -2496,16 +2575,16 @@
         <v>44</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>13</v>
@@ -2518,16 +2597,16 @@
         <v>45</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>13</v>
@@ -2540,16 +2619,16 @@
         <v>46</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>13</v>
@@ -2562,16 +2641,16 @@
         <v>47</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>26</v>
@@ -2584,16 +2663,16 @@
         <v>48</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>26</v>
@@ -2606,16 +2685,16 @@
         <v>49</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>26</v>
@@ -2628,16 +2707,16 @@
         <v>50</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>26</v>
@@ -2650,16 +2729,16 @@
         <v>51</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>26</v>
@@ -2667,19 +2746,54 @@
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
     </row>
+    <row r="65" spans="1:8" ht="19">
+      <c r="A65" s="11"/>
+      <c r="B65" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17"/>
+      <c r="G65" s="17"/>
+      <c r="H65" s="18"/>
+    </row>
+    <row r="66" spans="1:8" ht="40" customHeight="1">
+      <c r="A66" s="12">
+        <v>53</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:H64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="10">
+  <autoFilter ref="A3:H66" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="11">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B12:H12"/>
     <mergeCell ref="B55:H55"/>
     <mergeCell ref="B15:H15"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B51:H51"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <phoneticPr fontId="6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
